--- a/automation/hdb_immo_ginto_zugaenglichkeit/Meta_IMMO_Ginto.xlsx
+++ b/automation/hdb_immo_ginto_zugaenglichkeit/Meta_IMMO_Ginto.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sszgua\git\opendatazurich.github.io\automation\immo_ginto_zugaenglichkeit\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sszgua\git\opendatazurich.github.io\automation\hdb_immo_ginto_zugaenglichkeit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4261AFD5-DC80-4043-84DA-7E4275ACEA96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE9D1A57-82FF-4A85-85FD-F298F2AF862C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29925" yWindow="2760" windowWidth="21600" windowHeight="12585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15495" yWindow="5340" windowWidth="19785" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="metadata" sheetId="14" r:id="rId1"/>
@@ -2087,7 +2087,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>106</v>
+        <v>48</v>
       </c>
       <c r="E14" s="7"/>
       <c r="F14" s="7" t="s">
@@ -3124,26 +3124,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="637d3f4c-beee-42dd-a17b-93f7589025e5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="31d8624d-d3e1-4449-addd-518bfa42d279">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x01010036EB69643BC4D84A90CF31D6917ED8B0" ma:contentTypeVersion="17" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="e787fa9c9cb978e1d00e8cc5d4e605d2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="31d8624d-d3e1-4449-addd-518bfa42d279" xmlns:ns3="637d3f4c-beee-42dd-a17b-93f7589025e5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="369004915ca410f163a62304f925ff92" ns2:_="" ns3:_="">
     <xsd:import namespace="31d8624d-d3e1-4449-addd-518bfa42d279"/>
@@ -3392,32 +3372,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6056489-A7A4-4445-AFC5-87E5586E5E93}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="637d3f4c-beee-42dd-a17b-93f7589025e5"/>
-    <ds:schemaRef ds:uri="31d8624d-d3e1-4449-addd-518bfa42d279"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4B3AD83-9986-4E71-995F-A94C1CED6EB8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="637d3f4c-beee-42dd-a17b-93f7589025e5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="31d8624d-d3e1-4449-addd-518bfa42d279">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B249E2D-022F-440D-B037-6C32F5252DA3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3434,4 +3409,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4B3AD83-9986-4E71-995F-A94C1CED6EB8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6056489-A7A4-4445-AFC5-87E5586E5E93}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="637d3f4c-beee-42dd-a17b-93f7589025e5"/>
+    <ds:schemaRef ds:uri="31d8624d-d3e1-4449-addd-518bfa42d279"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>